--- a/measurements/data.xlsx
+++ b/measurements/data.xlsx
@@ -8,18 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repo\vpv\measurements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE43D2A-7AA2-4642-AE59-5A11B4C9F1C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E0938B-D576-4BB2-ABF2-1B0CF6AEC7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Температурная зависимость (3)" sheetId="7" r:id="rId1"/>
     <sheet name="Температурная зависимость (2)" sheetId="6" r:id="rId2"/>
-    <sheet name="Предварительные измерения" sheetId="4" r:id="rId3"/>
-    <sheet name="Метод ДШ" sheetId="1" r:id="rId4"/>
-    <sheet name="Лист2" sheetId="5" r:id="rId5"/>
-    <sheet name="Температурная зависимость" sheetId="3" r:id="rId6"/>
-    <sheet name="Черновик" sheetId="2" r:id="rId7"/>
+    <sheet name="Метод ДШ" sheetId="1" r:id="rId3"/>
+    <sheet name="Температурная зависимость" sheetId="3" r:id="rId4"/>
+    <sheet name="Черновик" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>L, мм</t>
   </si>
@@ -75,12 +73,6 @@
   </si>
   <si>
     <t>intercept</t>
-  </si>
-  <si>
-    <t>Диаметр горлышка, мм</t>
-  </si>
-  <si>
-    <t>Объём бутылки, мл</t>
   </si>
   <si>
     <t>sigma f, Гц</t>
@@ -224,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -250,9 +242,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4300,16 +4289,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
         <v>7</v>
@@ -4318,10 +4307,10 @@
         <v>8</v>
       </c>
       <c r="H1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -4551,10 +4540,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -4563,10 +4552,10 @@
         <v>8</v>
       </c>
       <c r="G1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -4769,35 +4758,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A80724C-3D69-497E-A4F5-19483014C354}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="36.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1">
-        <v>14.55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2">
-        <v>500</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5287,89 +5247,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37A0CAD-FCA7-424F-A9D8-68A683880CA7}">
-  <dimension ref="A2:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>35</v>
-      </c>
-      <c r="B2">
-        <v>131.4</v>
-      </c>
-      <c r="C2">
-        <f>B2*B2</f>
-        <v>17265.960000000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>45</v>
-      </c>
-      <c r="B3">
-        <v>133.4</v>
-      </c>
-      <c r="C3">
-        <f t="shared" ref="C3:C7" si="0">B3*B3</f>
-        <v>17795.560000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>55</v>
-      </c>
-      <c r="B4">
-        <v>134.30000000000001</v>
-      </c>
-      <c r="C4">
-        <f t="shared" si="0"/>
-        <v>18036.490000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>65</v>
-      </c>
-      <c r="B5">
-        <v>136.6</v>
-      </c>
-      <c r="C5">
-        <f t="shared" si="0"/>
-        <v>18659.559999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>75</v>
-      </c>
-      <c r="B6">
-        <v>138.5</v>
-      </c>
-      <c r="C6">
-        <f t="shared" si="0"/>
-        <v>19182.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>80</v>
-      </c>
-      <c r="B7">
-        <v>139.1</v>
-      </c>
-      <c r="C7">
-        <f t="shared" si="0"/>
-        <v>19348.809999999998</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15BE61EB-E579-4FD3-A110-4FA9DC715264}">
   <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5607,7 +5485,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB84B284-BC01-4B89-A236-E8B279AE980E}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5733,34 +5611,34 @@
       <c r="A8">
         <v>2.38</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="13">
         <v>127</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="13">
         <v>128.5</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="13">
         <v>130</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <v>131.4</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <v>133.5</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="13">
         <v>134.4</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <v>136.5</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="13">
         <v>138.5</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8" s="14">
         <v>138.9</v>
       </c>
     </row>

--- a/measurements/data.xlsx
+++ b/measurements/data.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repo\vpv\measurements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E0938B-D576-4BB2-ABF2-1B0CF6AEC7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE43D2A-7AA2-4642-AE59-5A11B4C9F1C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Температурная зависимость (3)" sheetId="7" r:id="rId1"/>
     <sheet name="Температурная зависимость (2)" sheetId="6" r:id="rId2"/>
-    <sheet name="Метод ДШ" sheetId="1" r:id="rId3"/>
-    <sheet name="Температурная зависимость" sheetId="3" r:id="rId4"/>
-    <sheet name="Черновик" sheetId="2" r:id="rId5"/>
+    <sheet name="Предварительные измерения" sheetId="4" r:id="rId3"/>
+    <sheet name="Метод ДШ" sheetId="1" r:id="rId4"/>
+    <sheet name="Лист2" sheetId="5" r:id="rId5"/>
+    <sheet name="Температурная зависимость" sheetId="3" r:id="rId6"/>
+    <sheet name="Черновик" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="18">
   <si>
     <t>L, мм</t>
   </si>
@@ -73,6 +75,12 @@
   </si>
   <si>
     <t>intercept</t>
+  </si>
+  <si>
+    <t>Диаметр горлышка, мм</t>
+  </si>
+  <si>
+    <t>Объём бутылки, мл</t>
   </si>
   <si>
     <t>sigma f, Гц</t>
@@ -216,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -242,6 +250,9 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4289,16 +4300,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F1" t="s">
         <v>7</v>
@@ -4307,10 +4318,10 @@
         <v>8</v>
       </c>
       <c r="H1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -4540,10 +4551,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -4552,10 +4563,10 @@
         <v>8</v>
       </c>
       <c r="G1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -4758,6 +4769,35 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A80724C-3D69-497E-A4F5-19483014C354}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1">
+        <v>14.55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5247,7 +5287,89 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37A0CAD-FCA7-424F-A9D8-68A683880CA7}">
+  <dimension ref="A2:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>35</v>
+      </c>
+      <c r="B2">
+        <v>131.4</v>
+      </c>
+      <c r="C2">
+        <f>B2*B2</f>
+        <v>17265.960000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>45</v>
+      </c>
+      <c r="B3">
+        <v>133.4</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C7" si="0">B3*B3</f>
+        <v>17795.560000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>55</v>
+      </c>
+      <c r="B4">
+        <v>134.30000000000001</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>18036.490000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>65</v>
+      </c>
+      <c r="B5">
+        <v>136.6</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>18659.559999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>75</v>
+      </c>
+      <c r="B6">
+        <v>138.5</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>19182.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>80</v>
+      </c>
+      <c r="B7">
+        <v>139.1</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>19348.809999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15BE61EB-E579-4FD3-A110-4FA9DC715264}">
   <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5485,7 +5607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB84B284-BC01-4B89-A236-E8B279AE980E}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5611,34 +5733,34 @@
       <c r="A8">
         <v>2.38</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="14">
         <v>127</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <v>128.5</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="14">
         <v>130</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <v>131.4</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="14">
         <v>133.5</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="14">
         <v>134.4</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="14">
         <v>136.5</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="14">
         <v>138.5</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="15">
         <v>138.9</v>
       </c>
     </row>
